--- a/tests/fixtures/synthetic/messy_headers/expenses.xlsx
+++ b/tests/fixtures/synthetic/messy_headers/expenses.xlsx
@@ -444,7 +444,7 @@
         </is>
       </c>
       <c r="E4">
-        <v>2042.35</v>
+        <v>3527.7</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="E7">
-        <v>2189.1</v>
+        <v>3781.18</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
         </is>
       </c>
       <c r="E10">
-        <v>9530.98</v>
+        <v>16462.61</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="E13">
-        <v>10215.81</v>
+        <v>17645.5</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="E15">
-        <v>2488.8</v>
+        <v>3479.03</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="E16">
-        <v>2216.19</v>
+        <v>3277.57</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="E19">
-        <v>1944.01</v>
+        <v>3357.84</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="E22">
-        <v>1998.73</v>
+        <v>3452.35</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="E25">
-        <v>9072.059999999999</v>
+        <v>15669.92</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="E28">
-        <v>9327.4</v>
+        <v>16110.96</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="E30">
-        <v>2377.88</v>
+        <v>3320.43</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="E31">
-        <v>2033.24</v>
+        <v>3002.32</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         </is>
       </c>
       <c r="E34">
-        <v>2334.71</v>
+        <v>4032.68</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="E37">
-        <v>2309.51</v>
+        <v>3989.16</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="E40">
-        <v>10895.3</v>
+        <v>18819.16</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         </is>
       </c>
       <c r="E43">
-        <v>10777.72</v>
+        <v>18616.07</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="E48">
-        <v>2832.12</v>
+        <v>3964.1</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         </is>
       </c>
       <c r="E49">
-        <v>2345.25</v>
+        <v>3465.01</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         </is>
       </c>
       <c r="E52">
-        <v>2381.99</v>
+        <v>4114.34</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         </is>
       </c>
       <c r="E55">
-        <v>2329.63</v>
+        <v>4023.91</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         </is>
       </c>
       <c r="E58">
-        <v>11115.94</v>
+        <v>19200.26</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="E61">
-        <v>10871.62</v>
+        <v>18778.25</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="E64">
-        <v>2933.22</v>
+        <v>4088.12</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         </is>
       </c>
       <c r="E65">
-        <v>2365.14</v>
+        <v>3494.66</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         </is>
       </c>
       <c r="E68">
-        <v>2551.1</v>
+        <v>4406.45</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="E71">
-        <v>2528.67</v>
+        <v>4367.71</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         </is>
       </c>
       <c r="E74">
-        <v>11905.15</v>
+        <v>20563.44</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="E77">
-        <v>11800.47</v>
+        <v>20382.63</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="E81">
-        <v>3101.66</v>
+        <v>4338.56</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="E82">
-        <v>2617.3</v>
+        <v>3843.32</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="E85">
-        <v>2538.63</v>
+        <v>4384.9</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         </is>
       </c>
       <c r="E88">
-        <v>2628.81</v>
+        <v>4540.68</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="E91">
-        <v>11846.93</v>
+        <v>20462.87</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="E94">
-        <v>12267.8</v>
+        <v>21189.84</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         </is>
       </c>
       <c r="E99">
-        <v>3076.13</v>
+        <v>4306.98</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         </is>
       </c>
       <c r="E100">
-        <v>2717.04</v>
+        <v>3991.62</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         </is>
       </c>
       <c r="E103">
-        <v>2664.47</v>
+        <v>4602.27</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -3694,7 +3694,7 @@
         </is>
       </c>
       <c r="E106">
-        <v>2782.93</v>
+        <v>4806.88</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         </is>
       </c>
       <c r="E109">
-        <v>12434.19</v>
+        <v>21477.24</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         </is>
       </c>
       <c r="E112">
-        <v>12987.01</v>
+        <v>22432.11</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         </is>
       </c>
       <c r="E118">
-        <v>3250.8</v>
+        <v>4542.66</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         </is>
       </c>
       <c r="E119">
-        <v>2919.86</v>
+        <v>4269.16</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="E122">
-        <v>2855.92</v>
+        <v>4932.96</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         </is>
       </c>
       <c r="E125">
-        <v>2871.03</v>
+        <v>4959.04</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         </is>
       </c>
       <c r="E128">
-        <v>13327.64</v>
+        <v>23020.48</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         </is>
       </c>
       <c r="E131">
-        <v>13398.12</v>
+        <v>23142.21</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="E136">
-        <v>3350.72</v>
+        <v>4735.41</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         </is>
       </c>
       <c r="E137">
-        <v>3014.47</v>
+        <v>4406.49</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         </is>
       </c>
       <c r="E140">
-        <v>2774.66</v>
+        <v>4792.6</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -4877,7 +4877,7 @@
         </is>
       </c>
       <c r="E143">
-        <v>2831.55</v>
+        <v>4890.86</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -4978,7 +4978,7 @@
         </is>
       </c>
       <c r="E146">
-        <v>12948.43</v>
+        <v>22365.47</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         </is>
       </c>
       <c r="E149">
-        <v>13213.9</v>
+        <v>22824.02</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         </is>
       </c>
       <c r="E156">
-        <v>3321.62</v>
+        <v>4666.91</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
         </is>
       </c>
       <c r="E157">
-        <v>3025.84</v>
+        <v>4398.72</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         </is>
       </c>
       <c r="E160">
-        <v>3058.2</v>
+        <v>5282.34</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         </is>
       </c>
       <c r="E163">
-        <v>3165.29</v>
+        <v>5467.31</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
         </is>
       </c>
       <c r="E166">
-        <v>14271.6</v>
+        <v>24650.94</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         </is>
       </c>
       <c r="E169">
-        <v>14771.34</v>
+        <v>25514.13</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         </is>
       </c>
       <c r="E173">
-        <v>3572.53</v>
+        <v>5055.3</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         </is>
       </c>
       <c r="E174">
-        <v>3311.08</v>
+        <v>4845.77</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
         </is>
       </c>
       <c r="E177">
-        <v>3033.34</v>
+        <v>5239.41</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         </is>
       </c>
       <c r="E180">
-        <v>3195.13</v>
+        <v>5518.86</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         </is>
       </c>
       <c r="E183">
-        <v>14155.6</v>
+        <v>24450.59</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         </is>
       </c>
       <c r="E186">
-        <v>14910.61</v>
+        <v>25754.69</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         </is>
       </c>
       <c r="E190">
-        <v>3590.08</v>
+        <v>5060.8</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
         </is>
       </c>
       <c r="E191">
-        <v>3414.92</v>
+        <v>4964.08</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         </is>
       </c>
       <c r="E194">
-        <v>3221.69</v>
+        <v>5564.73</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         </is>
       </c>
       <c r="E197">
-        <v>3296.98</v>
+        <v>5694.79</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         </is>
       </c>
       <c r="E200">
-        <v>15034.53</v>
+        <v>25968.74</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="E203">
-        <v>15385.92</v>
+        <v>26575.68</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         </is>
       </c>
       <c r="E209">
-        <v>3837.68</v>
+        <v>5399.71</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         </is>
       </c>
       <c r="E210">
-        <v>3684.21</v>
+        <v>5282.75</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         </is>
       </c>
       <c r="E213">
-        <v>3297.34</v>
+        <v>5695.41</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         </is>
       </c>
       <c r="E216">
-        <v>3422.45</v>
+        <v>5911.5</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="E219">
-        <v>15387.59</v>
+        <v>26578.57</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         </is>
       </c>
       <c r="E222">
-        <v>15971.41</v>
+        <v>27586.99</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         </is>
       </c>
       <c r="E227">
-        <v>3816.33</v>
+        <v>5415.04</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="E228">
-        <v>3774.28</v>
+        <v>5433.64</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
         </is>
       </c>
       <c r="E231">
-        <v>2957.93</v>
+        <v>5109.15</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         </is>
       </c>
       <c r="E234">
-        <v>3321.42</v>
+        <v>5737</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="E237">
-        <v>13803.68</v>
+        <v>23842.72</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         </is>
       </c>
       <c r="E240">
-        <v>15499.96</v>
+        <v>26772.65</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         </is>
       </c>
       <c r="E244">
-        <v>3456.26</v>
+        <v>4890.41</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
         </is>
       </c>
       <c r="E245">
-        <v>3671.22</v>
+        <v>5281.6</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         </is>
       </c>
       <c r="E248">
-        <v>3449.41</v>
+        <v>5958.07</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         </is>
       </c>
       <c r="E251">
-        <v>3760.65</v>
+        <v>6495.67</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         </is>
       </c>
       <c r="E254">
-        <v>16097.24</v>
+        <v>27804.33</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="E257">
-        <v>17549.71</v>
+        <v>30313.14</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="E261">
-        <v>4099.67</v>
+        <v>5772.11</v>
       </c>
       <c r="G261" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
         </is>
       </c>
       <c r="E262">
-        <v>4269.88</v>
+        <v>6093.23</v>
       </c>
       <c r="G262" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="E265">
-        <v>3513.37</v>
+        <v>6068.56</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         </is>
       </c>
       <c r="E268">
-        <v>3793.47</v>
+        <v>6552.35</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -8981,7 +8981,7 @@
         </is>
       </c>
       <c r="E271">
-        <v>16395.75</v>
+        <v>28319.93</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
         </is>
       </c>
       <c r="E274">
-        <v>17702.84</v>
+        <v>30577.64</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         </is>
       </c>
       <c r="E278">
-        <v>4399.8</v>
+        <v>6103.26</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         </is>
       </c>
       <c r="E279">
-        <v>4231.54</v>
+        <v>6070.8</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -9318,7 +9318,7 @@
         </is>
       </c>
       <c r="E282">
-        <v>3886.2</v>
+        <v>6712.53</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -9421,7 +9421,7 @@
         </is>
       </c>
       <c r="E285">
-        <v>4186.14</v>
+        <v>7230.6</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         </is>
       </c>
       <c r="E288">
-        <v>18135.6</v>
+        <v>31325.13</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         </is>
       </c>
       <c r="E291">
-        <v>19535.31</v>
+        <v>33742.81</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -9820,7 +9820,7 @@
         </is>
       </c>
       <c r="E297">
-        <v>4974.52</v>
+        <v>6858.74</v>
       </c>
       <c r="G297" t="inlineStr">
         <is>
@@ -9845,7 +9845,7 @@
         </is>
       </c>
       <c r="E298">
-        <v>4571.3</v>
+        <v>6600.94</v>
       </c>
       <c r="G298" t="inlineStr">
         <is>
@@ -9931,7 +9931,7 @@
         </is>
       </c>
       <c r="E301">
-        <v>3930.18</v>
+        <v>6788.5</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
         </is>
       </c>
       <c r="E304">
-        <v>4464.32</v>
+        <v>7711.1</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         </is>
       </c>
       <c r="E307">
-        <v>18340.86</v>
+        <v>31679.67</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         </is>
       </c>
       <c r="E310">
-        <v>20833.5</v>
+        <v>35985.13</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -10433,7 +10433,7 @@
         </is>
       </c>
       <c r="E316">
-        <v>5100.6</v>
+        <v>7006.14</v>
       </c>
       <c r="G316" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         </is>
       </c>
       <c r="E317">
-        <v>4718.82</v>
+        <v>6883.34</v>
       </c>
       <c r="G317" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         </is>
       </c>
       <c r="E320">
-        <v>4260.83</v>
+        <v>7359.61</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -10643,7 +10643,7 @@
         </is>
       </c>
       <c r="E323">
-        <v>4744.59</v>
+        <v>8195.200000000001</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -10744,7 +10744,7 @@
         </is>
       </c>
       <c r="E326">
-        <v>19883.86</v>
+        <v>34344.85</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -10847,7 +10847,7 @@
         </is>
       </c>
       <c r="E329">
-        <v>22141.41</v>
+        <v>38244.26</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -11083,7 +11083,7 @@
         </is>
       </c>
       <c r="E336">
-        <v>5424.8</v>
+        <v>7490.65</v>
       </c>
       <c r="G336" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
         </is>
       </c>
       <c r="E337">
-        <v>5216.61</v>
+        <v>7517.01</v>
       </c>
       <c r="G337" t="inlineStr">
         <is>
@@ -11192,7 +11192,7 @@
         </is>
       </c>
       <c r="E340">
-        <v>4539.27</v>
+        <v>7840.55</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -11293,7 +11293,7 @@
         </is>
       </c>
       <c r="E343">
-        <v>4845.72</v>
+        <v>8369.879999999999</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         </is>
       </c>
       <c r="E346">
-        <v>21183.24</v>
+        <v>36589.24</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -11495,7 +11495,7 @@
         </is>
       </c>
       <c r="E349">
-        <v>22613.35</v>
+        <v>39059.42</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         </is>
       </c>
       <c r="E354">
-        <v>5919.99</v>
+        <v>8120.85</v>
       </c>
       <c r="G354" t="inlineStr">
         <is>
@@ -11680,7 +11680,7 @@
         </is>
       </c>
       <c r="E355">
-        <v>5273.51</v>
+        <v>7622.95</v>
       </c>
       <c r="G355" t="inlineStr">
         <is>
@@ -11768,7 +11768,7 @@
         </is>
       </c>
       <c r="E358">
-        <v>4533.28</v>
+        <v>7830.22</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -11873,7 +11873,7 @@
         </is>
       </c>
       <c r="E361">
-        <v>4773.06</v>
+        <v>8244.379999999999</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="E364">
-        <v>21155.32</v>
+        <v>36541.01</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
         </is>
       </c>
       <c r="E367">
-        <v>22274.3</v>
+        <v>38473.79</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         </is>
       </c>
       <c r="E372">
-        <v>6053.92</v>
+        <v>8251.879999999999</v>
       </c>
       <c r="G372" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         </is>
       </c>
       <c r="E373">
-        <v>5112.39</v>
+        <v>7426.6</v>
       </c>
       <c r="G373" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         </is>
       </c>
       <c r="E376">
-        <v>4680.38</v>
+        <v>8084.3</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         </is>
       </c>
       <c r="E379">
-        <v>4842.14</v>
+        <v>8363.700000000001</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         </is>
       </c>
       <c r="E382">
-        <v>21841.78</v>
+        <v>37726.71</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         </is>
       </c>
       <c r="E385">
-        <v>22596.65</v>
+        <v>39030.58</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -12856,7 +12856,7 @@
         </is>
       </c>
       <c r="E391">
-        <v>6353.77</v>
+        <v>8623.049999999999</v>
       </c>
       <c r="G391" t="inlineStr">
         <is>
@@ -12879,7 +12879,7 @@
         </is>
       </c>
       <c r="E392">
-        <v>5225.4</v>
+        <v>7573.1</v>
       </c>
       <c r="G392" t="inlineStr">
         <is>
@@ -12965,7 +12965,7 @@
         </is>
       </c>
       <c r="E395">
-        <v>4771.1</v>
+        <v>8240.98</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -13068,7 +13068,7 @@
         </is>
       </c>
       <c r="E398">
-        <v>4913.42</v>
+        <v>8486.809999999999</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         </is>
       </c>
       <c r="E401">
-        <v>22265.11</v>
+        <v>38457.92</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -13270,7 +13270,7 @@
         </is>
       </c>
       <c r="E404">
-        <v>22929.28</v>
+        <v>39605.12</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -13438,7 +13438,7 @@
         </is>
       </c>
       <c r="E409">
-        <v>6337.67</v>
+        <v>8650.93</v>
       </c>
       <c r="G409" t="inlineStr">
         <is>
@@ -13461,7 +13461,7 @@
         </is>
       </c>
       <c r="E410">
-        <v>5150.21</v>
+        <v>7532.47</v>
       </c>
       <c r="G410" t="inlineStr">
         <is>
@@ -13547,7 +13547,7 @@
         </is>
       </c>
       <c r="E413">
-        <v>5247.58</v>
+        <v>9064</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -13650,7 +13650,7 @@
         </is>
       </c>
       <c r="E416">
-        <v>5405.62</v>
+        <v>9336.99</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -13751,7 +13751,7 @@
         </is>
       </c>
       <c r="E419">
-        <v>24488.71</v>
+        <v>42298.68</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -13850,7 +13850,7 @@
         </is>
       </c>
       <c r="E422">
-        <v>25226.25</v>
+        <v>43572.61</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         </is>
       </c>
       <c r="E426">
-        <v>6697.85</v>
+        <v>9242.139999999999</v>
       </c>
       <c r="G426" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         </is>
       </c>
       <c r="E427">
-        <v>5534.58</v>
+        <v>8155.49</v>
       </c>
       <c r="G427" t="inlineStr">
         <is>
@@ -14090,7 +14090,7 @@
         </is>
       </c>
       <c r="E430">
-        <v>5535.05</v>
+        <v>9560.540000000001</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -14191,7 +14191,7 @@
         </is>
       </c>
       <c r="E433">
-        <v>5617.85</v>
+        <v>9703.559999999999</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         </is>
       </c>
       <c r="E436">
-        <v>25830.23</v>
+        <v>44615.85</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         </is>
       </c>
       <c r="E439">
-        <v>26216.64</v>
+        <v>45283.29</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -14553,7 +14553,7 @@
         </is>
       </c>
       <c r="E444">
-        <v>6996.24</v>
+        <v>9679.9</v>
       </c>
       <c r="G444" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         </is>
       </c>
       <c r="E445">
-        <v>5745.14</v>
+        <v>8468.950000000001</v>
       </c>
       <c r="G445" t="inlineStr">
         <is>
@@ -14660,7 +14660,7 @@
         </is>
       </c>
       <c r="E448">
-        <v>5541.04</v>
+        <v>9570.889999999999</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         </is>
       </c>
       <c r="E451">
-        <v>5575</v>
+        <v>9629.549999999999</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -14864,7 +14864,7 @@
         </is>
       </c>
       <c r="E454">
-        <v>25858.2</v>
+        <v>44664.17</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         </is>
       </c>
       <c r="E457">
-        <v>26016.67</v>
+        <v>44937.88</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         </is>
       </c>
       <c r="E461">
-        <v>7038.6</v>
+        <v>9725.16</v>
       </c>
       <c r="G461" t="inlineStr">
         <is>
@@ -15121,7 +15121,7 @@
         </is>
       </c>
       <c r="E462">
-        <v>5631.63</v>
+        <v>8334.66</v>
       </c>
       <c r="G462" t="inlineStr">
         <is>
@@ -15205,7 +15205,7 @@
         </is>
       </c>
       <c r="E465">
-        <v>6336.53</v>
+        <v>10944.92</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -15304,7 +15304,7 @@
         </is>
       </c>
       <c r="E468">
-        <v>6219.87</v>
+        <v>10743.42</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -15403,7 +15403,7 @@
         </is>
       </c>
       <c r="E471">
-        <v>29570.49</v>
+        <v>51076.3</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         </is>
       </c>
       <c r="E474">
-        <v>29026.08</v>
+        <v>50135.96</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -15633,7 +15633,7 @@
         </is>
       </c>
       <c r="E478">
-        <v>7596.25</v>
+        <v>10668.51</v>
       </c>
       <c r="G478" t="inlineStr">
         <is>
@@ -15656,7 +15656,7 @@
         </is>
       </c>
       <c r="E479">
-        <v>6278.01</v>
+        <v>9293.709999999999</v>
       </c>
       <c r="G479" t="inlineStr">
         <is>
@@ -15742,7 +15742,7 @@
         </is>
       </c>
       <c r="E482">
-        <v>6183.12</v>
+        <v>10679.93</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         </is>
       </c>
       <c r="E485">
-        <v>6444.72</v>
+        <v>11131.79</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
         </is>
       </c>
       <c r="E488">
-        <v>28854.55</v>
+        <v>49839.67</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         </is>
       </c>
       <c r="E491">
-        <v>30075.37</v>
+        <v>51948.36</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -16180,7 +16180,7 @@
         </is>
       </c>
       <c r="E495">
-        <v>7136.05</v>
+        <v>10133.92</v>
       </c>
       <c r="G495" t="inlineStr">
         <is>
@@ -16203,7 +16203,7 @@
         </is>
       </c>
       <c r="E496">
-        <v>6449.06</v>
+        <v>9573.780000000001</v>
       </c>
       <c r="G496" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
         </is>
       </c>
       <c r="E499">
-        <v>6402.52</v>
+        <v>11058.9</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         </is>
       </c>
       <c r="E502">
-        <v>7000.73</v>
+        <v>12092.17</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         </is>
       </c>
       <c r="E505">
-        <v>29878.44</v>
+        <v>51608.22</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         </is>
       </c>
       <c r="E508">
-        <v>32670.08</v>
+        <v>56430.13</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -16690,7 +16690,7 @@
         </is>
       </c>
       <c r="E511">
-        <v>7383.1</v>
+        <v>10487.36</v>
       </c>
       <c r="G511" t="inlineStr">
         <is>
@@ -16713,7 +16713,7 @@
         </is>
       </c>
       <c r="E512">
-        <v>6991.61</v>
+        <v>10385.9</v>
       </c>
       <c r="G512" t="inlineStr">
         <is>
@@ -16799,7 +16799,7 @@
         </is>
       </c>
       <c r="E515">
-        <v>6283</v>
+        <v>10852.46</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -16898,7 +16898,7 @@
         </is>
       </c>
       <c r="E518">
-        <v>6813.28</v>
+        <v>11768.4</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         </is>
       </c>
       <c r="E521">
-        <v>29320.69</v>
+        <v>50644.82</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -17098,7 +17098,7 @@
         </is>
       </c>
       <c r="E524">
-        <v>31795.32</v>
+        <v>54919.19</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         </is>
       </c>
       <c r="E528">
-        <v>7363.99</v>
+        <v>10410.29</v>
       </c>
       <c r="G528" t="inlineStr">
         <is>
@@ -17254,7 +17254,7 @@
         </is>
       </c>
       <c r="E529">
-        <v>6742.06</v>
+        <v>10045.47</v>
       </c>
       <c r="G529" t="inlineStr">
         <is>
@@ -17340,7 +17340,7 @@
         </is>
       </c>
       <c r="E532">
-        <v>7150.09</v>
+        <v>12350.16</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -17441,7 +17441,7 @@
         </is>
       </c>
       <c r="E535">
-        <v>7082.51</v>
+        <v>12233.43</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         </is>
       </c>
       <c r="E538">
-        <v>33367.1</v>
+        <v>57634.08</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         </is>
       </c>
       <c r="E541">
-        <v>33051.72</v>
+        <v>57089.34</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -17772,7 +17772,7 @@
         </is>
       </c>
       <c r="E545">
-        <v>8271.969999999999</v>
+        <v>11738.68</v>
       </c>
       <c r="G545" t="inlineStr">
         <is>
@@ -17797,7 +17797,7 @@
         </is>
       </c>
       <c r="E546">
-        <v>6839.06</v>
+        <v>10273</v>
       </c>
       <c r="G546" t="inlineStr">
         <is>
@@ -17883,7 +17883,7 @@
         </is>
       </c>
       <c r="E549">
-        <v>7489.09</v>
+        <v>12935.71</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -17984,7 +17984,7 @@
         </is>
       </c>
       <c r="E552">
-        <v>7190.55</v>
+        <v>12420.04</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -18083,7 +18083,7 @@
         </is>
       </c>
       <c r="E555">
-        <v>34949.11</v>
+        <v>60366.64</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -18186,7 +18186,7 @@
         </is>
       </c>
       <c r="E558">
-        <v>33555.91</v>
+        <v>57960.2</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -18282,7 +18282,7 @@
         </is>
       </c>
       <c r="E561">
-        <v>8598.809999999999</v>
+        <v>12229.89</v>
       </c>
       <c r="G561" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         </is>
       </c>
       <c r="E562">
-        <v>7083.03</v>
+        <v>10569.36</v>
       </c>
       <c r="G562" t="inlineStr">
         <is>
@@ -18393,7 +18393,7 @@
         </is>
       </c>
       <c r="E565">
-        <v>7650.84</v>
+        <v>13215.09</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -18494,7 +18494,7 @@
         </is>
       </c>
       <c r="E568">
-        <v>7210.56</v>
+        <v>12454.61</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -18593,7 +18593,7 @@
         </is>
       </c>
       <c r="E571">
-        <v>35703.93</v>
+        <v>61670.43</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -18694,7 +18694,7 @@
         </is>
       </c>
       <c r="E574">
-        <v>33649.29</v>
+        <v>58121.51</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -18860,7 +18860,7 @@
         </is>
       </c>
       <c r="E579">
-        <v>8428.34</v>
+        <v>12137.84</v>
       </c>
       <c r="G579" t="inlineStr">
         <is>
@@ -18883,7 +18883,7 @@
         </is>
       </c>
       <c r="E580">
-        <v>7254.58</v>
+        <v>10750.61</v>
       </c>
       <c r="G580" t="inlineStr">
         <is>
@@ -18969,7 +18969,7 @@
         </is>
       </c>
       <c r="E583">
-        <v>8516.65</v>
+        <v>14710.58</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -19070,7 +19070,7 @@
         </is>
       </c>
       <c r="E586">
-        <v>8044.38</v>
+        <v>13894.84</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -19171,7 +19171,7 @@
         </is>
       </c>
       <c r="E589">
-        <v>39744.38</v>
+        <v>68649.38</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -19270,7 +19270,7 @@
         </is>
       </c>
       <c r="E592">
-        <v>37540.45</v>
+        <v>64842.59</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         </is>
       </c>
       <c r="E597">
-        <v>9383.65</v>
+        <v>13512.93</v>
       </c>
       <c r="G597" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         </is>
       </c>
       <c r="E598">
-        <v>7949.07</v>
+        <v>11849.38</v>
       </c>
       <c r="G598" t="inlineStr">
         <is>
@@ -19543,7 +19543,7 @@
         </is>
       </c>
       <c r="E601">
-        <v>8213.68</v>
+        <v>14187.27</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -19646,7 +19646,7 @@
         </is>
       </c>
       <c r="E604">
-        <v>8024.23</v>
+        <v>13860.03</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -19747,7 +19747,7 @@
         </is>
       </c>
       <c r="E607">
-        <v>38330.53</v>
+        <v>66207.27</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
         </is>
       </c>
       <c r="E610">
-        <v>37446.4</v>
+        <v>64680.14</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -20043,7 +20043,7 @@
         </is>
       </c>
       <c r="E616">
-        <v>9260.07</v>
+        <v>13242.47</v>
       </c>
       <c r="G616" t="inlineStr">
         <is>
@@ -20066,7 +20066,7 @@
         </is>
       </c>
       <c r="E617">
-        <v>8061.57</v>
+        <v>11952.11</v>
       </c>
       <c r="G617" t="inlineStr">
         <is>
@@ -20152,7 +20152,7 @@
         </is>
       </c>
       <c r="E620">
-        <v>8356.209999999999</v>
+        <v>14433.45</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -20253,7 +20253,7 @@
         </is>
       </c>
       <c r="E623">
-        <v>8589.4</v>
+        <v>14836.24</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         </is>
       </c>
       <c r="E626">
-        <v>38995.63</v>
+        <v>67356.09</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -20455,7 +20455,7 @@
         </is>
       </c>
       <c r="E629">
-        <v>40083.89</v>
+        <v>69235.8</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -20617,7 +20617,7 @@
         </is>
       </c>
       <c r="E634">
-        <v>9655.549999999999</v>
+        <v>13707.04</v>
       </c>
       <c r="G634" t="inlineStr">
         <is>
@@ -20640,7 +20640,7 @@
         </is>
       </c>
       <c r="E635">
-        <v>8916.27</v>
+        <v>13080.82</v>
       </c>
       <c r="G635" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
         </is>
       </c>
       <c r="E638">
-        <v>8637.76</v>
+        <v>14919.78</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -20823,7 +20823,7 @@
         </is>
       </c>
       <c r="E641">
-        <v>9353.1</v>
+        <v>16155.36</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -20924,7 +20924,7 @@
         </is>
       </c>
       <c r="E644">
-        <v>40309.57</v>
+        <v>69625.62</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -21025,7 +21025,7 @@
         </is>
       </c>
       <c r="E647">
-        <v>43647.82</v>
+        <v>75391.67999999999</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -21152,7 +21152,7 @@
         </is>
       </c>
       <c r="E651">
-        <v>10074.48</v>
+        <v>14262.48</v>
       </c>
       <c r="G651" t="inlineStr">
         <is>
@@ -21177,7 +21177,7 @@
         </is>
       </c>
       <c r="E652">
-        <v>9659.950000000001</v>
+        <v>14194.79</v>
       </c>
       <c r="G652" t="inlineStr">
         <is>
@@ -21263,7 +21263,7 @@
         </is>
       </c>
       <c r="E655">
-        <v>7883.3</v>
+        <v>13616.61</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -21364,7 +21364,7 @@
         </is>
       </c>
       <c r="E658">
-        <v>9052.700000000001</v>
+        <v>15636.48</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -21463,7 +21463,7 @@
         </is>
       </c>
       <c r="E661">
-        <v>36788.73</v>
+        <v>63544.17</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -21564,7 +21564,7 @@
         </is>
       </c>
       <c r="E664">
-        <v>42245.93</v>
+        <v>72970.25</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -21726,7 +21726,7 @@
         </is>
       </c>
       <c r="E669">
-        <v>9157.530000000001</v>
+        <v>12979.73</v>
       </c>
       <c r="G669" t="inlineStr">
         <is>
@@ -21749,7 +21749,7 @@
         </is>
       </c>
       <c r="E670">
-        <v>9203.35</v>
+        <v>13592.53</v>
       </c>
       <c r="G670" t="inlineStr">
         <is>
@@ -21835,7 +21835,7 @@
         </is>
       </c>
       <c r="E673">
-        <v>9303.49</v>
+        <v>16069.67</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -21936,7 +21936,7 @@
         </is>
       </c>
       <c r="E676">
-        <v>10491.74</v>
+        <v>18122.1</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -22039,7 +22039,7 @@
         </is>
       </c>
       <c r="E679">
-        <v>43416.3</v>
+        <v>74991.78</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -22138,7 +22138,7 @@
         </is>
       </c>
       <c r="E682">
-        <v>48961.45</v>
+        <v>84569.78</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -22370,7 +22370,7 @@
         </is>
       </c>
       <c r="E689">
-        <v>10720.02</v>
+        <v>15230.81</v>
       </c>
       <c r="G689" t="inlineStr">
         <is>
@@ -22395,7 +22395,7 @@
         </is>
       </c>
       <c r="E690">
-        <v>10580.96</v>
+        <v>15667.86</v>
       </c>
       <c r="G690" t="inlineStr">
         <is>
@@ -22483,7 +22483,7 @@
         </is>
       </c>
       <c r="E693">
-        <v>9701.389999999999</v>
+        <v>16756.94</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -22582,7 +22582,7 @@
         </is>
       </c>
       <c r="E696">
-        <v>10304.42</v>
+        <v>17798.54</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -22685,7 +22685,7 @@
         </is>
       </c>
       <c r="E699">
-        <v>45273.13</v>
+        <v>78199.05</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -22784,7 +22784,7 @@
         </is>
       </c>
       <c r="E702">
-        <v>48087.27</v>
+        <v>83059.83</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -22981,7 +22981,7 @@
         </is>
       </c>
       <c r="E708">
-        <v>11028.26</v>
+        <v>15731.96</v>
       </c>
       <c r="G708" t="inlineStr">
         <is>
@@ -23004,7 +23004,7 @@
         </is>
       </c>
       <c r="E709">
-        <v>10385.88</v>
+        <v>15381.96</v>
       </c>
       <c r="G709" t="inlineStr">
         <is>
@@ -23090,7 +23090,7 @@
         </is>
       </c>
       <c r="E712">
-        <v>10662.5</v>
+        <v>18417.04</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         </is>
       </c>
       <c r="E715">
-        <v>10109.51</v>
+        <v>17461.88</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -23292,7 +23292,7 @@
         </is>
       </c>
       <c r="E718">
-        <v>49758.32</v>
+        <v>85946.17999999999</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -23395,7 +23395,7 @@
         </is>
       </c>
       <c r="E721">
-        <v>47177.7</v>
+        <v>81488.75999999999</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -23493,7 +23493,7 @@
         </is>
       </c>
       <c r="E724">
-        <v>12015.55</v>
+        <v>17185.25</v>
       </c>
       <c r="G724" t="inlineStr">
         <is>
@@ -23518,7 +23518,7 @@
         </is>
       </c>
       <c r="E725">
-        <v>10402.89</v>
+        <v>15304.47</v>
       </c>
       <c r="G725" t="inlineStr">
         <is>
@@ -23604,7 +23604,7 @@
         </is>
       </c>
       <c r="E728">
-        <v>10545.7</v>
+        <v>18215.3</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -23707,7 +23707,7 @@
         </is>
       </c>
       <c r="E731">
-        <v>9857.83</v>
+        <v>17027.15</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -23810,7 +23810,7 @@
         </is>
       </c>
       <c r="E734">
-        <v>49213.28</v>
+        <v>85004.75</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -23913,7 +23913,7 @@
         </is>
       </c>
       <c r="E737">
-        <v>46003.19</v>
+        <v>79460.05</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -23974,7 +23974,7 @@
         </is>
       </c>
       <c r="E739">
-        <v>12122.05</v>
+        <v>17235.12</v>
       </c>
       <c r="G739" t="inlineStr">
         <is>
@@ -23997,7 +23997,7 @@
         </is>
       </c>
       <c r="E740">
-        <v>10230.84</v>
+        <v>15010.39</v>
       </c>
       <c r="G740" t="inlineStr">
         <is>
@@ -24085,7 +24085,7 @@
         </is>
       </c>
       <c r="E743">
-        <v>10993.87</v>
+        <v>18989.42</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -24184,7 +24184,7 @@
         </is>
       </c>
       <c r="E746">
-        <v>10834.67</v>
+        <v>18714.43</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -24287,7 +24287,7 @@
         </is>
       </c>
       <c r="E749">
-        <v>51304.75</v>
+        <v>88617.28999999999</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -24390,7 +24390,7 @@
         </is>
       </c>
       <c r="E752">
-        <v>50561.79</v>
+        <v>87334</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         </is>
       </c>
       <c r="E757">
-        <v>12970.21</v>
+        <v>18300.57</v>
       </c>
       <c r="G757" t="inlineStr">
         <is>
@@ -24573,7 +24573,7 @@
         </is>
       </c>
       <c r="E758">
-        <v>11001.15</v>
+        <v>16254.33</v>
       </c>
       <c r="G758" t="inlineStr">
         <is>
@@ -24659,7 +24659,7 @@
         </is>
       </c>
       <c r="E761">
-        <v>11251.81</v>
+        <v>19434.95</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -24758,7 +24758,7 @@
         </is>
       </c>
       <c r="E764">
-        <v>11092.75</v>
+        <v>19160.2</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         </is>
       </c>
       <c r="E767">
-        <v>52508.46</v>
+        <v>90696.42999999999</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -24960,7 +24960,7 @@
         </is>
       </c>
       <c r="E770">
-        <v>51766.16</v>
+        <v>89414.27</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         </is>
       </c>
       <c r="E775">
-        <v>13351.84</v>
+        <v>18807.26</v>
       </c>
       <c r="G775" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         </is>
       </c>
       <c r="E776">
-        <v>11978.03</v>
+        <v>17356.33</v>
       </c>
       <c r="G776" t="inlineStr">
         <is>
@@ -25233,7 +25233,7 @@
         </is>
       </c>
       <c r="E779">
-        <v>10929.54</v>
+        <v>18878.29</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -25336,7 +25336,7 @@
         </is>
       </c>
       <c r="E782">
-        <v>11270.1</v>
+        <v>19466.54</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -25437,7 +25437,7 @@
         </is>
       </c>
       <c r="E785">
-        <v>51004.5</v>
+        <v>88098.69</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -25540,7 +25540,7 @@
         </is>
       </c>
       <c r="E788">
-        <v>52593.81</v>
+        <v>90843.85000000001</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -25673,7 +25673,7 @@
         </is>
       </c>
       <c r="E792">
-        <v>13229.38</v>
+        <v>18528.55</v>
       </c>
       <c r="G792" t="inlineStr">
         <is>
@@ -25698,7 +25698,7 @@
         </is>
       </c>
       <c r="E793">
-        <v>12021.75</v>
+        <v>17486.04</v>
       </c>
       <c r="G793" t="inlineStr">
         <is>
@@ -25784,7 +25784,7 @@
         </is>
       </c>
       <c r="E796">
-        <v>10995.32</v>
+        <v>18991.91</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -25885,7 +25885,7 @@
         </is>
       </c>
       <c r="E799">
-        <v>11898.91</v>
+        <v>20552.67</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -25988,7 +25988,7 @@
         </is>
       </c>
       <c r="E802">
-        <v>51311.48</v>
+        <v>88628.91</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -26089,7 +26089,7 @@
         </is>
       </c>
       <c r="E805">
-        <v>55528.27</v>
+        <v>95912.46000000001</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -26251,7 +26251,7 @@
         </is>
       </c>
       <c r="E810">
-        <v>13315.2</v>
+        <v>18646.27</v>
       </c>
       <c r="G810" t="inlineStr">
         <is>
@@ -26276,7 +26276,7 @@
         </is>
       </c>
       <c r="E811">
-        <v>12458.13</v>
+        <v>18227.3</v>
       </c>
       <c r="G811" t="inlineStr">
         <is>
@@ -26362,7 +26362,7 @@
         </is>
       </c>
       <c r="E814">
-        <v>10314.67</v>
+        <v>17816.24</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -26465,7 +26465,7 @@
         </is>
       </c>
       <c r="E817">
-        <v>11862.51</v>
+        <v>20489.79</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -26568,7 +26568,7 @@
         </is>
       </c>
       <c r="E820">
-        <v>48135.12</v>
+        <v>83142.47</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -26671,7 +26671,7 @@
         </is>
       </c>
       <c r="E823">
-        <v>55358.38</v>
+        <v>95619.02</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -26798,7 +26798,7 @@
         </is>
       </c>
       <c r="E827">
-        <v>13089.08</v>
+        <v>18090.13</v>
       </c>
       <c r="G827" t="inlineStr">
         <is>
@@ -26823,7 +26823,7 @@
         </is>
       </c>
       <c r="E828">
-        <v>12202.17</v>
+        <v>17953.69</v>
       </c>
       <c r="G828" t="inlineStr">
         <is>
@@ -26911,7 +26911,7 @@
         </is>
       </c>
       <c r="E831">
-        <v>10943.91</v>
+        <v>18903.11</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -27010,7 +27010,7 @@
         </is>
       </c>
       <c r="E834">
-        <v>12549.88</v>
+        <v>21677.07</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -27109,7 +27109,7 @@
         </is>
       </c>
       <c r="E837">
-        <v>51071.57</v>
+        <v>88214.52</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -27210,7 +27210,7 @@
         </is>
       </c>
       <c r="E840">
-        <v>58566.11</v>
+        <v>101159.64</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -27407,7 +27407,7 @@
         </is>
       </c>
       <c r="E846">
-        <v>14322.01</v>
+        <v>19628.14</v>
       </c>
       <c r="G846" t="inlineStr">
         <is>
@@ -27430,7 +27430,7 @@
         </is>
       </c>
       <c r="E847">
-        <v>12663.23</v>
+        <v>18748.02</v>
       </c>
       <c r="G847" t="inlineStr">
         <is>

--- a/tests/fixtures/synthetic/messy_headers/expenses.xlsx
+++ b/tests/fixtures/synthetic/messy_headers/expenses.xlsx
@@ -10948,7 +10948,7 @@
         </is>
       </c>
       <c r="E332">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
